--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484531_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484531_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDÉS</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5753</v>
+        <v>1.9304</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5753</v>
+        <v>0.6202</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.3102</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5753</v>
+        <v>1.721</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3251</v>
+        <v>-0.2116</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2502</v>
+        <v>1.9326</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5753</v>
+        <v>2.1198</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3251</v>
+        <v>1.2446</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2502</v>
+        <v>0.8752</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0.3988</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-1.4563</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.0575</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0.1363</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-0.4001</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.2637</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0.0208</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>E. NAVARRO VALDÉS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4138</v>
+        <v>1.5753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0293</v>
+        <v>1.5753</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3845</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.721</v>
+        <v>1.5753</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2116</v>
+        <v>0.3251</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9326</v>
+        <v>1.2502</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1198</v>
+        <v>1.5753</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2446</v>
+        <v>0.3251</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8752</v>
+        <v>1.2502</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3988</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4563</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0575</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6529</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9909</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3381</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0208</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. FORNER LUCEA</t>
+          <t>L. JURADO TRAVER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.517</v>
+        <v>0.6863</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1792</v>
+        <v>-0.2357</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6622</v>
+        <v>0.922</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8552</v>
+        <v>3.8642</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0187</v>
+        <v>2.3353</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1635</v>
+        <v>1.5289</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1325</v>
+        <v>3.596</v>
       </c>
       <c r="K4" t="n">
-        <v>0.065</v>
+        <v>2.8361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0674</v>
+        <v>0.76</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9876</v>
+        <v>0.2682</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0837</v>
+        <v>-0.5008</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0961</v>
+        <v>0.7689</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.1154</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.3795</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2202</v>
+        <v>-0.7164</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1526</v>
+        <v>0.3369</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2566</v>
+        <v>-0.9658</v>
       </c>
       <c r="W4" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0104</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. JURADO TRAVER</t>
+          <t>O. FORNER LUCEA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1227</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6754</v>
+        <v>1.2754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7982</v>
+        <v>-0.7366</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8642</v>
+        <v>-0.8552</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3353</v>
+        <v>-1.0187</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5289</v>
+        <v>0.1635</v>
       </c>
       <c r="J5" t="n">
-        <v>3.596</v>
+        <v>0.1325</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8361</v>
+        <v>0.065</v>
       </c>
       <c r="L5" t="n">
-        <v>0.76</v>
+        <v>0.0674</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2682</v>
+        <v>-0.9876</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5008</v>
+        <v>-1.0837</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7689</v>
+        <v>0.0961</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8326</v>
+        <v>0.1833</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1154</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9431</v>
+        <v>-0.0458</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1561</v>
+        <v>-0.1241</v>
       </c>
       <c r="U5" t="n">
-        <v>0.213</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9658</v>
+        <v>1.2566</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9658</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1121</v>
+        <v>0.4367</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8572</v>
+        <v>-0.706</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9693000000000001</v>
+        <v>1.1427</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0638</v>
@@ -922,13 +922,13 @@
         <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5254</v>
+        <v>-0.2008</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8808</v>
+        <v>-0.7296</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3554</v>
+        <v>0.5288</v>
       </c>
       <c r="V6" t="n">
         <v>2.5339</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1973</v>
+        <v>-0.151</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3344</v>
+        <v>-0.9909</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1371</v>
+        <v>0.8399</v>
       </c>
       <c r="G7" t="n">
         <v>1.2216</v>
@@ -1000,13 +1000,13 @@
         <v>1.6493</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2068</v>
+        <v>0.253</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6056</v>
+        <v>-0.2621</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8123</v>
+        <v>0.5151</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3428</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1189</v>
+        <v>-1.5228</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6118</v>
+        <v>-1.9414</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4929</v>
+        <v>0.4186</v>
       </c>
       <c r="G8" t="n">
         <v>2.3674</v>
@@ -1078,13 +1078,13 @@
         <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3909</v>
+        <v>-0.013</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0159</v>
+        <v>-0.3137</v>
       </c>
       <c r="U8" t="n">
-        <v>0.375</v>
+        <v>0.3007</v>
       </c>
       <c r="V8" t="n">
         <v>-0.945</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7711</v>
+        <v>-2.1195</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3878</v>
+        <v>-0.9097</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3832</v>
+        <v>-1.2098</v>
       </c>
       <c r="G9" t="n">
         <v>2.4748</v>
@@ -1156,13 +1156,13 @@
         <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2989</v>
+        <v>-0.0496</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2043</v>
+        <v>-0.7262</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5032</v>
+        <v>0.6766</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2461</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9375</v>
+        <v>-3.6901</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6626</v>
+        <v>-0.4152</v>
       </c>
       <c r="F10" t="n">
         <v>-3.2749</v>
@@ -1234,10 +1234,10 @@
         <v>0.1833</v>
       </c>
       <c r="S10" t="n">
-        <v>0.092</v>
+        <v>0.3394</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1652</v>
+        <v>0.0822</v>
       </c>
       <c r="U10" t="n">
         <v>0.2572</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1356</v>
+        <v>-6.4567</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4901</v>
+        <v>-6.8608</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3545</v>
+        <v>0.4041</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6665</v>
@@ -1312,13 +1312,13 @@
         <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1069</v>
+        <v>-0.2142</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2043</v>
+        <v>-0.575</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3113</v>
+        <v>0.3608</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2774</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.419499999999999</v>
+        <v>-8.772599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.2355</v>
+        <v>-8.588800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1838</v>
+        <v>-0.1837999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>8.326499999999999</v>
@@ -1390,13 +1390,13 @@
         <v>10.9955</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0935</v>
+        <v>-0.4468</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.4115</v>
+        <v>-3.765000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3181</v>
+        <v>3.318000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9079</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2139</v>
+        <v>4.0988</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5175</v>
+        <v>4.2291</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3036</v>
+        <v>-0.1302</v>
       </c>
       <c r="G13" t="n">
         <v>3.0523</v>
@@ -1468,13 +1468,13 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0779</v>
+        <v>-0.0371</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2368</v>
+        <v>-0.0516</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1589</v>
+        <v>0.0145</v>
       </c>
       <c r="V13" t="n">
         <v>1.267</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7933</v>
+        <v>4.046</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3277</v>
+        <v>2.5838</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4656</v>
+        <v>1.4622</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5174</v>
+        <v>-1.315</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6652</v>
+        <v>-0.6069</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.1827</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1767</v>
+        <v>0.9901</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6532</v>
+        <v>0.9287</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8299</v>
+        <v>0.0614</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3407</v>
+        <v>-2.3051</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0121</v>
+        <v>-1.5356</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3528</v>
+        <v>-0.7695</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5656</v>
+        <v>3.1154</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.6651</v>
+        <v>3.1154</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1012</v>
+        <v>0.0128</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6931</v>
+        <v>-0.6391</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4081</v>
+        <v>0.6519</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6439</v>
+        <v>2.2328</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9109</v>
+        <v>2.2328</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5157</v>
+        <v>3.0299</v>
       </c>
       <c r="E15" t="n">
-        <v>2.103</v>
+        <v>0.3662</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4126</v>
+        <v>2.6638</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.315</v>
+        <v>-0.5174</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6069</v>
+        <v>1.6652</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-2.1827</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9901</v>
+        <v>-0.1767</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9287</v>
+        <v>1.6532</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0614</v>
+        <v>-1.8299</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3051</v>
+        <v>-0.3407</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5356</v>
+        <v>0.0121</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7695</v>
+        <v>-0.3528</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1154</v>
+        <v>2.5656</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1154</v>
+        <v>3.6651</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5175</v>
+        <v>0.3379</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1199</v>
+        <v>-0.2684</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6024</v>
+        <v>0.6063</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2328</v>
+        <v>0.6439</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2328</v>
+        <v>1.9109</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9297</v>
+        <v>3.0101</v>
       </c>
       <c r="E16" t="n">
-        <v>1.611</v>
+        <v>0.4781</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3187</v>
+        <v>2.532</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1874</v>
+        <v>0.8768</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3251</v>
+        <v>3.7294</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8623</v>
+        <v>-2.8526</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1951</v>
+        <v>2.9593</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3527</v>
+        <v>4.7217</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5478</v>
+        <v>-1.7625</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9923</v>
+        <v>-2.0825</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6778</v>
+        <v>-0.9923</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3145</v>
+        <v>-1.0902</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4661</v>
+        <v>0.3665</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0995</v>
+        <v>-3.8484</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5656</v>
+        <v>4.2149</v>
       </c>
       <c r="S16" t="n">
-        <v>3.028</v>
+        <v>-0.1337</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3168</v>
+        <v>-0.8552</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7113</v>
+        <v>0.7215</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6231</v>
+        <v>1.9005</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5889</v>
+        <v>2.2224</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9658</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3093</v>
+        <v>1.1755</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0988</v>
+        <v>0.6495</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4081</v>
+        <v>0.526</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8768</v>
+        <v>-2.1874</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7294</v>
+        <v>-0.3251</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.8526</v>
+        <v>-1.8623</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9593</v>
+        <v>-0.1951</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7217</v>
+        <v>0.3527</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.7625</v>
+        <v>-0.5478</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0825</v>
+        <v>-1.9923</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9923</v>
+        <v>-0.6778</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0902</v>
+        <v>-1.3145</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3665</v>
+        <v>1.4661</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8484</v>
+        <v>-1.0995</v>
       </c>
       <c r="R17" t="n">
-        <v>4.2149</v>
+        <v>2.5656</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8345</v>
+        <v>1.2737</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4321</v>
+        <v>0.3552</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5976</v>
+        <v>0.9185</v>
       </c>
       <c r="V17" t="n">
-        <v>1.9005</v>
+        <v>0.6231</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2224</v>
+        <v>1.5889</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3219</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2593</v>
+        <v>0.4516</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1736</v>
+        <v>-1.9813</v>
       </c>
       <c r="F18" t="n">
         <v>2.4329</v>
@@ -1858,10 +1858,10 @@
         <v>4.3982</v>
       </c>
       <c r="S18" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.2647</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7911</v>
+        <v>-0.5988</v>
       </c>
       <c r="U18" t="n">
         <v>0.8635</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9161</v>
+        <v>-0.2094</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4229</v>
+        <v>-1.0383</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5068</v>
+        <v>0.8289</v>
       </c>
       <c r="G20" t="n">
         <v>-1.753</v>
@@ -2014,13 +2014,13 @@
         <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8124</v>
+        <v>-0.1058</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6425</v>
+        <v>-0.2579</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1699</v>
+        <v>0.1521</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1924</v>
+        <v>-0.9039</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2231</v>
+        <v>-1.9346</v>
       </c>
       <c r="F21" t="n">
         <v>1.0307</v>
@@ -2092,10 +2092,10 @@
         <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4035</v>
+        <v>-0.115</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5513</v>
+        <v>-0.2628</v>
       </c>
       <c r="U21" t="n">
         <v>0.1478</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3051</v>
+        <v>-2.3823</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2686</v>
+        <v>-2.1725</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0364</v>
+        <v>-0.2099</v>
       </c>
       <c r="G22" t="n">
         <v>0.4881</v>
@@ -2170,13 +2170,13 @@
         <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0092</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2021</v>
+        <v>-0.106</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2886</v>
+        <v>0.1152</v>
       </c>
       <c r="V22" t="n">
         <v>-2.5131</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0882</v>
+        <v>-2.7968</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1767</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9115</v>
+        <v>-1.8124</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8209</v>
@@ -2248,13 +2248,13 @@
         <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6496</v>
+        <v>-0.3582</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5784</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1211</v>
+        <v>0.2202</v>
       </c>
       <c r="V23" t="n">
         <v>-1.267</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.4192</v>
+        <v>9.419299999999996</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1837999999999995</v>
+        <v>0.1838999999999994</v>
       </c>
       <c r="F24" t="n">
-        <v>9.235399999999998</v>
+        <v>9.2355</v>
       </c>
       <c r="G24" t="n">
         <v>-8.3263</v>
       </c>
       <c r="H24" t="n">
-        <v>6.2579</v>
+        <v>6.257900000000002</v>
       </c>
       <c r="I24" t="n">
         <v>-14.5845</v>
@@ -2311,7 +2311,7 @@
         <v>-14.1832</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.205699999999999</v>
+        <v>-5.2057</v>
       </c>
       <c r="O24" t="n">
         <v>-8.977399999999999</v>
@@ -2329,10 +2329,10 @@
         <v>1.0934</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.3181</v>
+        <v>-3.318099999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>4.4116</v>
+        <v>4.411499999999999</v>
       </c>
       <c r="V24" t="n">
         <v>2.907999999999999</v>
